--- a/reports/forex/ggmi/2026-06/output/GGMI-June-2026-Performance-Report.xlsx
+++ b/reports/forex/ggmi/2026-06/output/GGMI-June-2026-Performance-Report.xlsx
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>34555.83</v>
+        <v>35026</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>7679074</v>
@@ -847,13 +847,13 @@
         <v>0.001291</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>42</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>822.76</v>
+        <v>833.95</v>
       </c>
     </row>
     <row r="17">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>119922.35</v>
+        <v>120392.52</v>
       </c>
       <c r="C18" s="18" t="n">
         <v>69891221</v>
@@ -941,7 +941,7 @@
     <row r="22" ht="82" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>June was the biggest GGMI media month of 2026: $119,922 across four channels, up 56% from May, delivering 69.9M impressions and 449.8K clicks. Application volume followed the spend. Search produced 50 submitted applications at $513 each (up from 33 in May) and Azerion added 42 at $823, holding efficiency through a 27% budget increase. Site traffic recovered with the spend: 9,236 Mexico sessions (+61% vs May) and 5,838 unique visitors (+125%). The recovery is real but bought. Media drove essentially all of the June gain while organic search sat at its low, down 75% since January per Search Console. We are approximately 31% into the annual GGMI budget.</t>
+          <t>June was the biggest GGMI media month of 2026: $120,393 across four channels, up 53% from May, delivering 69.9M impressions and 449.8K clicks. Application volume followed the spend. Search produced 50 submitted applications at $513 each (up from 33 in May) and Azerion added 42 at $834, holding efficiency through a 20% budget increase. Site traffic recovered with the spend: 9,236 Mexico sessions (+61% vs May) and 5,838 unique visitors (+125%). The recovery is real but bought. Media drove essentially all of the June gain while organic search sat at its low, down 75% since January per Search Console. We are approximately 31% into the annual GGMI budget.</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>•  Azerion applications rose 14% (37 to 42) on a 27% budget increase; application starts nearly doubled to 440; Global Market converted at $407.</t>
+          <t>•  Azerion applications rose 14% (37 to 42) on a 20% budget increase; application starts nearly doubled to 440; Global Market converted at $412.</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>•  Concentrate Azerion budget on converting ad sets; Conversion_Commodities spent $4,072 with zero applications.</t>
+          <t>•  Concentrate Azerion budget on converting ad sets; Conversion_Commodities spent $4,128 with zero applications.</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>34555.83</v>
+        <v>35026</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>7679074</v>
@@ -1271,10 +1271,10 @@
         <v>0.001291</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>3.49</v>
+        <v>3.53</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
         </is>
       </c>
       <c r="I7" s="7" t="n">
-        <v>822.76</v>
+        <v>833.95</v>
       </c>
       <c r="J7" s="21" t="n">
         <v>0.6847</v>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>119922.35</v>
+        <v>120392.52</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>69891221</v>
@@ -1430,7 +1430,7 @@
         <v>0.6065</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>0.214</v>
+        <v>0.2131</v>
       </c>
     </row>
     <row r="14">
@@ -1452,7 +1452,7 @@
         <v>2.9124</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0.2162</v>
+        <v>0.2153</v>
       </c>
     </row>
     <row r="15">
@@ -1474,7 +1474,7 @@
         <v>0.2564</v>
       </c>
       <c r="F15" s="21" t="n">
-        <v>0.2817</v>
+        <v>0.2806</v>
       </c>
     </row>
     <row r="16">
@@ -1484,19 +1484,19 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>10215</v>
+        <v>10776.83</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>27257.72</v>
+        <v>29302.05</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>34555.83</v>
+        <v>35026</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>0.2677</v>
+        <v>0.1953</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>0.2882</v>
+        <v>0.2909</v>
       </c>
     </row>
     <row r="17">
@@ -1506,691 +1506,683 @@
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>45736.1</v>
+        <v>46297.93</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>76745.78</v>
+        <v>78790.11</v>
       </c>
       <c r="D17" s="17" t="n">
-        <v>119922.35</v>
+        <v>120392.52</v>
       </c>
       <c r="E17" s="23" t="n">
-        <v>0.5626</v>
+        <v>0.528</v>
       </c>
       <c r="F17" s="23" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>May Quantcast uses the client-reconciled $26,890. Azerion is raw vendor spend in all months (see Data Notes).</t>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Primary Conversions by Channel (per-channel definitions; never summed)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>Primary Conversions by Channel (per-channel definitions; never summed)</t>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>June CPA</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Definition</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Bing (SA360)</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>513.17</v>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Submitted applications</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Held</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Pixel events; held pending validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Quantcast</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>View-through (directional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Azerion</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>833.95</v>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Submitted applications (vendor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Bing Campaigns (June)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Campaign</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Avg CPC</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Apps</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>AO Generic (policy test)</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>13508.22</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>164946</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>11020</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0.06680999999999999</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G28" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>500.3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Brand + Generic</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n">
+        <v>8154.4</v>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>195341</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>7559</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>0.038696</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>906.04</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Platform Intercept</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>3995.99</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>106295</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>2901</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0.027292</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G30" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>285.43</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>25658.61</v>
+      </c>
+      <c r="C31" s="18" t="n">
+        <v>466582</v>
+      </c>
+      <c r="D31" s="18" t="n">
+        <v>21480</v>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>0.046037</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="G31" s="18" t="n">
+        <v>50</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>513.17</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Azerion Ad Sets (June)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Ad Set</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Apps</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>CPA</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>Viewability</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Experience</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>9118.440000000001</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>1999118</v>
+      </c>
+      <c r="D35" s="8" t="n">
+        <v>2499</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>828.95</v>
+      </c>
+      <c r="G35" s="21" t="n">
+        <v>0.6958</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Global Market</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n">
+        <v>4124.43</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>904236</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>1134</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>412.44</v>
+      </c>
+      <c r="G36" s="22" t="n">
+        <v>0.6758999999999999</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TradeForex</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>4220.74</v>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>925349</v>
+      </c>
+      <c r="D37" s="8" t="n">
+        <v>1140</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>602.96</v>
+      </c>
+      <c r="G37" s="21" t="n">
+        <v>0.6863</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>Language Broker</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n">
+        <v>4994.19</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>1094921</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>1510</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>713.46</v>
+      </c>
+      <c r="G38" s="22" t="n">
+        <v>0.6745</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Conversion_Instruments</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>4210.91</v>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>923196</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>1144</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>1052.73</v>
+      </c>
+      <c r="G39" s="21" t="n">
+        <v>0.6831</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>Spanish Platform</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>4229.49</v>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>927269</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>1309</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>1409.83</v>
+      </c>
+      <c r="G40" s="22" t="n">
+        <v>0.6723</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Conversion_Commodities</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>4127.85</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>904985</v>
+      </c>
+      <c r="D41" s="8" t="n">
+        <v>1174</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="n">
+        <v>0.6939</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>35026</v>
+      </c>
+      <c r="C42" s="18" t="n">
+        <v>7679074</v>
+      </c>
+      <c r="D42" s="18" t="n">
+        <v>9910</v>
+      </c>
+      <c r="E42" s="18" t="n">
+        <v>42</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>833.95</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <v>0.6847</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Site Traffic — GA4 Mexico, monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>May</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>June</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>June CPA</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Bing (SA360)</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>33</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>513.17</v>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>Submitted applications</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>Held</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="inlineStr">
-        <is>
-          <t>Pixel events; held pending validation</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Quantcast</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="10" t="inlineStr">
-        <is>
-          <t>View-through (directional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Azerion</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>42</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>822.76</v>
-      </c>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>Submitted applications (vendor)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Bing Campaigns (June)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Campaign</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>Avg CPC</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>Apps</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>CPA</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>AO Generic (policy test)</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n">
-        <v>13508.22</v>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>164946</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>11020</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>0.06680999999999999</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="H29" s="7" t="n">
-        <v>500.3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>Brand + Generic</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="n">
-        <v>8154.4</v>
-      </c>
-      <c r="C30" s="13" t="n">
-        <v>195341</v>
-      </c>
-      <c r="D30" s="13" t="n">
-        <v>7559</v>
-      </c>
-      <c r="E30" s="14" t="n">
-        <v>0.038696</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="G30" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>906.04</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Platform Intercept</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="n">
-        <v>3995.99</v>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>106295</v>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>2901</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>0.027292</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>285.43</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="n">
-        <v>25658.61</v>
-      </c>
-      <c r="C32" s="18" t="n">
-        <v>466582</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>21480</v>
-      </c>
-      <c r="E32" s="24" t="n">
-        <v>0.046037</v>
-      </c>
-      <c r="F32" s="17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="G32" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="H32" s="17" t="n">
-        <v>513.17</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Azerion Ad Sets (June)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>Ad Set</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Spend</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Impressions</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Clicks</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Apps</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>CPA</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>Viewability</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Experience</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="n">
-        <v>8996.030000000001</v>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>1999118</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>2499</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>817.8200000000001</v>
-      </c>
-      <c r="G36" s="21" t="n">
-        <v>0.6958</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>Global Market</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="n">
-        <v>4069.06</v>
-      </c>
-      <c r="C37" s="13" t="n">
-        <v>904236</v>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>1134</v>
-      </c>
-      <c r="E37" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <v>406.91</v>
-      </c>
-      <c r="G37" s="22" t="n">
-        <v>0.6758999999999999</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TradeForex</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="n">
-        <v>4164.07</v>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>925349</v>
-      </c>
-      <c r="D38" s="8" t="n">
-        <v>1140</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>594.87</v>
-      </c>
-      <c r="G38" s="21" t="n">
-        <v>0.6863</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Language Broker</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="n">
-        <v>4927.14</v>
-      </c>
-      <c r="C39" s="13" t="n">
-        <v>1094921</v>
-      </c>
-      <c r="D39" s="13" t="n">
-        <v>1510</v>
-      </c>
-      <c r="E39" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <v>703.88</v>
-      </c>
-      <c r="G39" s="22" t="n">
-        <v>0.6745</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Conversion_Instruments</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="n">
-        <v>4154.38</v>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>923196</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>1144</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="7" t="n">
-        <v>1038.6</v>
-      </c>
-      <c r="G40" s="21" t="n">
-        <v>0.6831</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
-        <is>
-          <t>Spanish Platform</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="n">
-        <v>4172.71</v>
-      </c>
-      <c r="C41" s="13" t="n">
-        <v>927269</v>
-      </c>
-      <c r="D41" s="13" t="n">
-        <v>1309</v>
-      </c>
-      <c r="E41" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>1390.9</v>
-      </c>
-      <c r="G41" s="22" t="n">
-        <v>0.6723</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Conversion_Commodities</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="n">
-        <v>4072.43</v>
-      </c>
-      <c r="C42" s="8" t="n">
-        <v>904985</v>
-      </c>
-      <c r="D42" s="8" t="n">
-        <v>1174</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="21" t="n">
-        <v>0.6939</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="n">
-        <v>34555.83</v>
-      </c>
-      <c r="C43" s="18" t="n">
-        <v>7679074</v>
-      </c>
-      <c r="D43" s="18" t="n">
-        <v>9910</v>
-      </c>
-      <c r="E43" s="18" t="n">
-        <v>42</v>
-      </c>
-      <c r="F43" s="17" t="n">
-        <v>822.76</v>
-      </c>
-      <c r="G43" s="23" t="n">
-        <v>0.6847</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>Site Traffic — GA4 Mexico, monthly</t>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>Jun</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>Jan</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Feb</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>Mar</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>Apr</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>May</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr">
-        <is>
-          <t>Jun</t>
-        </is>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Sessions</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>9380</v>
+      </c>
+      <c r="C46" s="8" t="n">
+        <v>22229</v>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>12614</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>7577</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>5751</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>9236</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Sessions</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="n">
-        <v>9380</v>
-      </c>
-      <c r="C47" s="8" t="n">
-        <v>22229</v>
-      </c>
-      <c r="D47" s="8" t="n">
-        <v>12614</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>7577</v>
-      </c>
-      <c r="F47" s="8" t="n">
-        <v>5751</v>
-      </c>
-      <c r="G47" s="8" t="n">
-        <v>9236</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Unique visitors</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n">
+      <c r="B47" s="13" t="n">
         <v>4651</v>
       </c>
-      <c r="C48" s="13" t="n">
+      <c r="C47" s="13" t="n">
         <v>14172</v>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D47" s="13" t="n">
         <v>6554</v>
       </c>
-      <c r="E48" s="13" t="n">
+      <c r="E47" s="13" t="n">
         <v>3366</v>
       </c>
-      <c r="F48" s="13" t="n">
+      <c r="F47" s="13" t="n">
         <v>2592</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="G47" s="13" t="n">
         <v>5838</v>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>June sessions +61% vs May; unique visitors +125% vs May and +26% vs January. February reflects a single paid flight and is not a valid baseline (see Diagnostics).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="8">
+    <mergeCell ref="A44:J44"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A45:J45"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A27:J27"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A19:J19"/>
     <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2717,7 +2709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2727,7 +2719,7 @@
     <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Data Notes — Basis, Corrections, Rules</t>
+          <t>Data Notes — Definitions &amp; Rules</t>
         </is>
       </c>
     </row>
@@ -2782,82 +2774,58 @@
     <row r="7" ht="43" customHeight="1">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t>Azerion spend basis</t>
+          <t>Search geo</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Raw vendor spend in all months (June $34,555.83; May $27,257.72). The May report stated Azerion at $29,302 on a fee-inclusive basis; comparisons here use the raw basis consistently.</t>
+          <t>51% of June search spend served Mexico; 49% ($12,637) served out-of-market users. The June 3 exclusion is active; the Mexico presence-only restriction completes the fix.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="27" t="inlineStr">
         <is>
-          <t>Quantcast May basis</t>
+          <t>Azerion geo</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>May uses the client-reconciled $26,890 (not the platform-pulled $25,013.56). June is the platform Budget Delivered figure, $33,784.20.</t>
+          <t>Country-level delivery confirmation requested from the vendor (early July); Mexico-only certification pending reply.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="43" customHeight="1">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>Search geo</t>
+          <t>SA360-GA4 link</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>51% of June search spend served Mexico; 49% ($12,637) served out-of-market users. The June 3 exclusion is active; the Mexico presence-only restriction completes the fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+          <t>The search account is not linked to GA4 property 508849216, leaving 2,451 June Mexico sessions (27%) unattributed. Once linked, July reporting will restate paid search larger; we will flag the restatement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
       <c r="A10" s="27" t="inlineStr">
         <is>
-          <t>Azerion geo</t>
+          <t>Revenue / ROAS</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Country-level delivery confirmation requested from the vendor (early July); Mexico-only certification pending reply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="43" customHeight="1">
+          <t>Not tracked on any channel; excluded from this report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>SA360-GA4 link</t>
+          <t>Sources</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>The search account is not linked to GA4 property 508849216, leaving 2,451 June Mexico sessions (27%) unattributed. Once linked, July reporting will restate paid search larger; we will flag the restatement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="27" t="inlineStr">
-        <is>
-          <t>Revenue / ROAS</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>Not tracked on any channel; excluded from this report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>Sources</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>SA360, Meta, Quantcast platform APIs; Azerion vendor workbook; GA4 property 508849216; Search Console. Pulled July 7, 2026.</t>
         </is>
